--- a/data/semanas/319_pe.xlsx
+++ b/data/semanas/319_pe.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL17"/>
+  <dimension ref="A1:AL29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1593,7 +1593,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>16861795</v>
+        <v>16896414</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -1602,22 +1602,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>419 - CENTRO 5 PE</t>
+          <t>435 - JARDIM PRIMOR- PE</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Q008</t>
+          <t>Q021</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Avenida ANTONIO JOAO</t>
+          <t>Rua SALGADO FILHO</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2643 - OU</t>
+          <t>32 - 2 - C</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1632,12 +1632,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>12/08/2026 08:38</t>
+          <t>12/08/2026 08:01</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>12/08/2026 08:50</t>
+          <t>12/08/2026 08:11</t>
         </is>
       </c>
       <c r="K9" t="n">
@@ -1654,13 +1654,13 @@
         </is>
       </c>
       <c r="N9" s="2" t="n">
-        <v>46246.35972222222</v>
+        <v>46246.33402777778</v>
       </c>
       <c r="O9" s="2" t="n">
-        <v>46246.36805555555</v>
+        <v>46246.34097222222</v>
       </c>
       <c r="P9" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="Q9" s="3" t="n">
         <v>46246</v>
@@ -1693,7 +1693,7 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>80880</v>
+        <v>78660</v>
       </c>
       <c r="AB9" t="b">
         <v>0</v>
@@ -1706,7 +1706,7 @@
         <v>8</v>
       </c>
       <c r="AF9" t="n">
-        <v>518</v>
+        <v>481</v>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
@@ -1731,7 +1731,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>16859701</v>
+        <v>16896415</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -1740,22 +1740,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>421 - IPANEMA - PE</t>
+          <t>435 - JARDIM PRIMOR- PE</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Q028</t>
+          <t>Q019</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Travessa DOS PODERES</t>
+          <t>Avenida DA FLORA</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>81 - OU</t>
+          <t>113 - 3 - C</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1770,12 +1770,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>12/08/2026 08:44</t>
+          <t>12/08/2026 08:13</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>12/08/2026 09:04</t>
+          <t>12/08/2026 08:36</t>
         </is>
       </c>
       <c r="K10" t="n">
@@ -1792,13 +1792,13 @@
         </is>
       </c>
       <c r="N10" s="2" t="n">
-        <v>46246.36388888889</v>
+        <v>46246.34236111111</v>
       </c>
       <c r="O10" s="2" t="n">
-        <v>46246.37777777778</v>
+        <v>46246.35833333333</v>
       </c>
       <c r="P10" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="Q10" s="3" t="n">
         <v>46246</v>
@@ -1831,7 +1831,7 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>360</v>
+        <v>720</v>
       </c>
       <c r="AB10" t="b">
         <v>0</v>
@@ -1844,7 +1844,7 @@
         <v>8</v>
       </c>
       <c r="AF10" t="n">
-        <v>524</v>
+        <v>493</v>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
@@ -1869,7 +1869,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>16872584</v>
+        <v>16861795</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -1878,22 +1878,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>414 - PARQUE DOS ERVAIS - PE</t>
+          <t>419 - CENTRO 5 PE</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Q012</t>
+          <t>Q008</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Rua 18 DE JULHO</t>
+          <t>Avenida ANTONIO JOAO</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>240 - C</t>
+          <t>2643 - OU</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1908,12 +1908,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>12/08/2026 09:03</t>
+          <t>12/08/2026 08:38</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>12/08/2026 09:17</t>
+          <t>12/08/2026 08:50</t>
         </is>
       </c>
       <c r="K11" t="n">
@@ -1930,13 +1930,13 @@
         </is>
       </c>
       <c r="N11" s="2" t="n">
-        <v>46246.37708333333</v>
+        <v>46246.35972222222</v>
       </c>
       <c r="O11" s="2" t="n">
-        <v>46246.38680555556</v>
+        <v>46246.36805555555</v>
       </c>
       <c r="P11" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="Q11" s="3" t="n">
         <v>46246</v>
@@ -1969,7 +1969,7 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1140</v>
+        <v>1500</v>
       </c>
       <c r="AB11" t="b">
         <v>0</v>
@@ -1979,10 +1979,10 @@
       </c>
       <c r="AD11" t="inlineStr"/>
       <c r="AE11" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AF11" t="n">
-        <v>543</v>
+        <v>518</v>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
@@ -2007,7 +2007,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>16859702</v>
+        <v>16896416</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -2016,22 +2016,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>413 - BAIRRO DA GRANJA - PE</t>
+          <t>414 - PARQUE DOS ERVAIS - PE</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Q024</t>
+          <t>Q020</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Rua VENCESLAU BRAZ</t>
+          <t>Rua PARAGUAI</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>146 - C</t>
+          <t>426 - 2 - C</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -2046,12 +2046,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>12/08/2026 09:20</t>
+          <t>12/08/2026 08:39</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>12/08/2026 09:32</t>
+          <t>12/08/2026 08:59</t>
         </is>
       </c>
       <c r="K12" t="n">
@@ -2068,13 +2068,13 @@
         </is>
       </c>
       <c r="N12" s="2" t="n">
-        <v>46246.38888888889</v>
+        <v>46246.36041666667</v>
       </c>
       <c r="O12" s="2" t="n">
-        <v>46246.39722222222</v>
+        <v>46246.37430555555</v>
       </c>
       <c r="P12" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="Q12" s="3" t="n">
         <v>46246</v>
@@ -2092,7 +2092,7 @@
         <v>0</v>
       </c>
       <c r="V12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W12" t="b">
         <v>0</v>
@@ -2107,7 +2107,7 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1020</v>
+        <v>60</v>
       </c>
       <c r="AB12" t="b">
         <v>0</v>
@@ -2117,10 +2117,10 @@
       </c>
       <c r="AD12" t="inlineStr"/>
       <c r="AE12" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AF12" t="n">
-        <v>560</v>
+        <v>519</v>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
@@ -2145,7 +2145,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>16872585</v>
+        <v>16859701</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -2154,22 +2154,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>408 - PARQUE DE EXPOSIÇOES - PE</t>
+          <t>421 - IPANEMA - PE</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Q029</t>
+          <t>Q028</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Rua CARLOS RONCATTI</t>
+          <t>Travessa DOS PODERES</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>789 - C</t>
+          <t>81 - OU</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -2184,12 +2184,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>12/08/2026 09:24</t>
+          <t>12/08/2026 08:44</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>12/08/2026 09:47</t>
+          <t>12/08/2026 09:04</t>
         </is>
       </c>
       <c r="K13" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="N13" s="2" t="n">
-        <v>46246.39166666667</v>
+        <v>46246.36388888889</v>
       </c>
       <c r="O13" s="2" t="n">
-        <v>46246.40763888889</v>
+        <v>46246.37777777778</v>
       </c>
       <c r="P13" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="Q13" s="3" t="n">
         <v>46246</v>
@@ -2245,7 +2245,7 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>240</v>
+        <v>300</v>
       </c>
       <c r="AB13" t="b">
         <v>0</v>
@@ -2255,10 +2255,10 @@
       </c>
       <c r="AD13" t="inlineStr"/>
       <c r="AE13" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AF13" t="n">
-        <v>564</v>
+        <v>524</v>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
@@ -2283,7 +2283,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>16859703</v>
+        <v>16896417</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -2292,22 +2292,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>408 - PARQUE DE EXPOSIÇOES - PE</t>
+          <t>414 - PARQUE DOS ERVAIS - PE</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Q029</t>
+          <t>Q009</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Rua CARLOS RONCATTI</t>
+          <t>Avenida INTERNACIONAL</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>789 - C</t>
+          <t>703 - C</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -2322,12 +2322,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>12/08/2026 09:39</t>
+          <t>12/08/2026 09:00</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>12/08/2026 09:51</t>
+          <t>12/08/2026 09:15</t>
         </is>
       </c>
       <c r="K14" t="n">
@@ -2344,13 +2344,13 @@
         </is>
       </c>
       <c r="N14" s="2" t="n">
-        <v>46246.40208333333</v>
+        <v>46246.375</v>
       </c>
       <c r="O14" s="2" t="n">
-        <v>46246.41041666667</v>
+        <v>46246.38541666666</v>
       </c>
       <c r="P14" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="Q14" s="3" t="n">
         <v>46246</v>
@@ -2383,7 +2383,7 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>900</v>
+        <v>960</v>
       </c>
       <c r="AB14" t="b">
         <v>0</v>
@@ -2396,7 +2396,7 @@
         <v>9</v>
       </c>
       <c r="AF14" t="n">
-        <v>579</v>
+        <v>540</v>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
@@ -2421,7 +2421,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>16871591</v>
+        <v>16872584</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -2430,22 +2430,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>403 - JARDIM UNIVERSITARIO - PE</t>
+          <t>414 - PARQUE DOS ERVAIS - PE</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Q031</t>
+          <t>Q012</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Rua OLINTHO CARDINAL DE JESUS</t>
+          <t>Rua 18 DE JULHO</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>855 - 2 - C</t>
+          <t>240 - C</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -2460,12 +2460,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>12/08/2026 15:19</t>
+          <t>12/08/2026 09:03</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>12/08/2026 15:33</t>
+          <t>12/08/2026 09:17</t>
         </is>
       </c>
       <c r="K15" t="n">
@@ -2482,10 +2482,10 @@
         </is>
       </c>
       <c r="N15" s="2" t="n">
-        <v>46246.63819444444</v>
+        <v>46246.37708333333</v>
       </c>
       <c r="O15" s="2" t="n">
-        <v>46246.64791666667</v>
+        <v>46246.38680555556</v>
       </c>
       <c r="P15" t="n">
         <v>14</v>
@@ -2521,7 +2521,7 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>20400</v>
+        <v>180</v>
       </c>
       <c r="AB15" t="b">
         <v>0</v>
@@ -2531,14 +2531,14 @@
       </c>
       <c r="AD15" t="inlineStr"/>
       <c r="AE15" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="AF15" t="n">
-        <v>919</v>
+        <v>543</v>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>Tarde</t>
+          <t>Manhã</t>
         </is>
       </c>
       <c r="AH15" t="b">
@@ -2559,7 +2559,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>16871592</v>
+        <v>16896418</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -2568,22 +2568,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>403 - JARDIM UNIVERSITARIO - PE</t>
+          <t>414 - PARQUE DOS ERVAIS - PE</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Q023</t>
+          <t>Q001</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Avenida VINÍCIUS SOARES DO NASCIMENTO</t>
+          <t>Avenida INTERNACIONAL</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>410 - 1 - C</t>
+          <t>510 - 1 - C</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>12/08/2026 15:35</t>
+          <t>12/08/2026 09:17</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>12/08/2026 15:51</t>
+          <t>12/08/2026 09:32</t>
         </is>
       </c>
       <c r="K16" t="n">
@@ -2620,13 +2620,13 @@
         </is>
       </c>
       <c r="N16" s="2" t="n">
-        <v>46246.64930555555</v>
+        <v>46246.38680555556</v>
       </c>
       <c r="O16" s="2" t="n">
-        <v>46246.66041666667</v>
+        <v>46246.39722222222</v>
       </c>
       <c r="P16" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="Q16" s="3" t="n">
         <v>46246</v>
@@ -2644,7 +2644,7 @@
         <v>0</v>
       </c>
       <c r="V16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W16" t="b">
         <v>0</v>
@@ -2659,7 +2659,7 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>960</v>
+        <v>840</v>
       </c>
       <c r="AB16" t="b">
         <v>0</v>
@@ -2669,14 +2669,14 @@
       </c>
       <c r="AD16" t="inlineStr"/>
       <c r="AE16" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="AF16" t="n">
-        <v>935</v>
+        <v>557</v>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>Tarde</t>
+          <t>Manhã</t>
         </is>
       </c>
       <c r="AH16" t="b">
@@ -2697,7 +2697,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>16871593</v>
+        <v>16859702</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -2706,22 +2706,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>406 - JARDIM PRIMAVERA - PE</t>
+          <t>413 - BAIRRO DA GRANJA - PE</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Q030</t>
+          <t>Q024</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Rua VASCO DA GAMA</t>
+          <t>Rua VENCESLAU BRAZ</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>327 - 5 - C</t>
+          <t>146 - C</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -2736,12 +2736,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>12/08/2026 15:57</t>
+          <t>12/08/2026 09:20</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>12/08/2026 16:07</t>
+          <t>12/08/2026 09:32</t>
         </is>
       </c>
       <c r="K17" t="n">
@@ -2758,13 +2758,13 @@
         </is>
       </c>
       <c r="N17" s="2" t="n">
-        <v>46246.66458333333</v>
+        <v>46246.38888888889</v>
       </c>
       <c r="O17" s="2" t="n">
-        <v>46246.67152777778</v>
+        <v>46246.39722222222</v>
       </c>
       <c r="P17" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="Q17" s="3" t="n">
         <v>46246</v>
@@ -2797,7 +2797,7 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1320</v>
+        <v>180</v>
       </c>
       <c r="AB17" t="b">
         <v>0</v>
@@ -2807,14 +2807,14 @@
       </c>
       <c r="AD17" t="inlineStr"/>
       <c r="AE17" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="AF17" t="n">
-        <v>957</v>
+        <v>560</v>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>Tarde</t>
+          <t>Manhã</t>
         </is>
       </c>
       <c r="AH17" t="b">
@@ -2830,6 +2830,1666 @@
         <v>1</v>
       </c>
       <c r="AL17" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>16872585</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>PONTO ESTRATÉGICO</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>408 - PARQUE DE EXPOSIÇOES - PE</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Q029</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Rua CARLOS RONCATTI</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>789 - C</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Ponto Estratégico</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>12/08/2026 09:24</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>12/08/2026 09:47</t>
+        </is>
+      </c>
+      <c r="K18" t="n">
+        <v>1031</v>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>Antonio Cezar Marques</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>Ponto Estratégico</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="n">
+        <v>46246.39166666667</v>
+      </c>
+      <c r="O18" s="2" t="n">
+        <v>46246.40763888889</v>
+      </c>
+      <c r="P18" t="n">
+        <v>23</v>
+      </c>
+      <c r="Q18" s="3" t="n">
+        <v>46246</v>
+      </c>
+      <c r="R18" t="n">
+        <v>319</v>
+      </c>
+      <c r="S18" t="n">
+        <v>32</v>
+      </c>
+      <c r="T18" t="b">
+        <v>0</v>
+      </c>
+      <c r="U18" t="b">
+        <v>0</v>
+      </c>
+      <c r="V18" t="b">
+        <v>1</v>
+      </c>
+      <c r="W18" t="b">
+        <v>0</v>
+      </c>
+      <c r="X18" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y18" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>240</v>
+      </c>
+      <c r="AB18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD18" t="inlineStr"/>
+      <c r="AE18" t="n">
+        <v>9</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>564</v>
+      </c>
+      <c r="AG18" t="inlineStr">
+        <is>
+          <t>Manhã</t>
+        </is>
+      </c>
+      <c r="AH18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK18" t="b">
+        <v>1</v>
+      </c>
+      <c r="AL18" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>16896419</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>PONTO ESTRATÉGICO</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>411 - JARDIM AEROPORTO - PE</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Q009</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Rua AEROPORTO CONGONHAS</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>535 - C</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Ponto Estratégico</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>12/08/2026 09:38</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>12/08/2026 10:02</t>
+        </is>
+      </c>
+      <c r="K19" t="n">
+        <v>1031</v>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>Antonio Cezar Marques</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>Ponto Estratégico</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="n">
+        <v>46246.40138888889</v>
+      </c>
+      <c r="O19" s="2" t="n">
+        <v>46246.41805555556</v>
+      </c>
+      <c r="P19" t="n">
+        <v>24</v>
+      </c>
+      <c r="Q19" s="3" t="n">
+        <v>46246</v>
+      </c>
+      <c r="R19" t="n">
+        <v>319</v>
+      </c>
+      <c r="S19" t="n">
+        <v>32</v>
+      </c>
+      <c r="T19" t="b">
+        <v>0</v>
+      </c>
+      <c r="U19" t="b">
+        <v>0</v>
+      </c>
+      <c r="V19" t="b">
+        <v>1</v>
+      </c>
+      <c r="W19" t="b">
+        <v>0</v>
+      </c>
+      <c r="X19" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y19" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>840</v>
+      </c>
+      <c r="AB19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD19" t="inlineStr"/>
+      <c r="AE19" t="n">
+        <v>9</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>578</v>
+      </c>
+      <c r="AG19" t="inlineStr">
+        <is>
+          <t>Manhã</t>
+        </is>
+      </c>
+      <c r="AH19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK19" t="b">
+        <v>1</v>
+      </c>
+      <c r="AL19" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>16859703</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>PONTO ESTRATÉGICO</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>408 - PARQUE DE EXPOSIÇOES - PE</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Q029</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Rua CARLOS RONCATTI</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>789 - C</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Ponto Estratégico</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>12/08/2026 09:39</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>12/08/2026 09:51</t>
+        </is>
+      </c>
+      <c r="K20" t="n">
+        <v>1031</v>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>Antonio Cezar Marques</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>Ponto Estratégico</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="n">
+        <v>46246.40208333333</v>
+      </c>
+      <c r="O20" s="2" t="n">
+        <v>46246.41041666667</v>
+      </c>
+      <c r="P20" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q20" s="3" t="n">
+        <v>46246</v>
+      </c>
+      <c r="R20" t="n">
+        <v>319</v>
+      </c>
+      <c r="S20" t="n">
+        <v>32</v>
+      </c>
+      <c r="T20" t="b">
+        <v>0</v>
+      </c>
+      <c r="U20" t="b">
+        <v>0</v>
+      </c>
+      <c r="V20" t="b">
+        <v>0</v>
+      </c>
+      <c r="W20" t="b">
+        <v>0</v>
+      </c>
+      <c r="X20" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y20" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>60</v>
+      </c>
+      <c r="AB20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD20" t="inlineStr"/>
+      <c r="AE20" t="n">
+        <v>9</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>579</v>
+      </c>
+      <c r="AG20" t="inlineStr">
+        <is>
+          <t>Manhã</t>
+        </is>
+      </c>
+      <c r="AH20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK20" t="b">
+        <v>1</v>
+      </c>
+      <c r="AL20" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>16896420</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>PONTO ESTRATÉGICO</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>403 - JARDIM UNIVERSITARIO - PE</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Q030</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Rua OLINTHO CARDINAL DE JESUS</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>138 - C</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Ponto Estratégico</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>12/08/2026 15:19</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>12/08/2026 15:30</t>
+        </is>
+      </c>
+      <c r="K21" t="n">
+        <v>1031</v>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>Antonio Cezar Marques</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>Ponto Estratégico</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="n">
+        <v>46246.63819444444</v>
+      </c>
+      <c r="O21" s="2" t="n">
+        <v>46246.64583333334</v>
+      </c>
+      <c r="P21" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q21" s="3" t="n">
+        <v>46246</v>
+      </c>
+      <c r="R21" t="n">
+        <v>319</v>
+      </c>
+      <c r="S21" t="n">
+        <v>32</v>
+      </c>
+      <c r="T21" t="b">
+        <v>0</v>
+      </c>
+      <c r="U21" t="b">
+        <v>0</v>
+      </c>
+      <c r="V21" t="b">
+        <v>0</v>
+      </c>
+      <c r="W21" t="b">
+        <v>0</v>
+      </c>
+      <c r="X21" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y21" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>20400</v>
+      </c>
+      <c r="AB21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC21" t="b">
+        <v>1</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>15</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>919</v>
+      </c>
+      <c r="AG21" t="inlineStr">
+        <is>
+          <t>Tarde</t>
+        </is>
+      </c>
+      <c r="AH21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK21" t="b">
+        <v>1</v>
+      </c>
+      <c r="AL21" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>16871591</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>PONTO ESTRATÉGICO</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>403 - JARDIM UNIVERSITARIO - PE</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Q031</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Rua OLINTHO CARDINAL DE JESUS</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>855 - 2 - C</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Ponto Estratégico</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>12/08/2026 15:19</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>12/08/2026 15:33</t>
+        </is>
+      </c>
+      <c r="K22" t="n">
+        <v>1031</v>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>Antonio Cezar Marques</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>Ponto Estratégico</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="n">
+        <v>46246.63819444444</v>
+      </c>
+      <c r="O22" s="2" t="n">
+        <v>46246.64791666667</v>
+      </c>
+      <c r="P22" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q22" s="3" t="n">
+        <v>46246</v>
+      </c>
+      <c r="R22" t="n">
+        <v>319</v>
+      </c>
+      <c r="S22" t="n">
+        <v>32</v>
+      </c>
+      <c r="T22" t="b">
+        <v>0</v>
+      </c>
+      <c r="U22" t="b">
+        <v>0</v>
+      </c>
+      <c r="V22" t="b">
+        <v>0</v>
+      </c>
+      <c r="W22" t="b">
+        <v>0</v>
+      </c>
+      <c r="X22" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y22" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB22" t="b">
+        <v>1</v>
+      </c>
+      <c r="AC22" t="b">
+        <v>1</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>15</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>919</v>
+      </c>
+      <c r="AG22" t="inlineStr">
+        <is>
+          <t>Tarde</t>
+        </is>
+      </c>
+      <c r="AH22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK22" t="b">
+        <v>1</v>
+      </c>
+      <c r="AL22" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>16883260</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>PONTO ESTRATÉGICO</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>408 - PARQUE DE EXPOSIÇOES - PE</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Q022</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Rua SOILO DE FREITAS</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>488 - C</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Ponto Estratégico</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>12/08/2026 15:24</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>12/08/2026 15:41</t>
+        </is>
+      </c>
+      <c r="K23" t="n">
+        <v>1031</v>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>Antonio Cezar Marques</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>Ponto Estratégico</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="n">
+        <v>46246.64166666667</v>
+      </c>
+      <c r="O23" s="2" t="n">
+        <v>46246.65347222222</v>
+      </c>
+      <c r="P23" t="n">
+        <v>17</v>
+      </c>
+      <c r="Q23" s="3" t="n">
+        <v>46246</v>
+      </c>
+      <c r="R23" t="n">
+        <v>319</v>
+      </c>
+      <c r="S23" t="n">
+        <v>32</v>
+      </c>
+      <c r="T23" t="b">
+        <v>0</v>
+      </c>
+      <c r="U23" t="b">
+        <v>0</v>
+      </c>
+      <c r="V23" t="b">
+        <v>1</v>
+      </c>
+      <c r="W23" t="b">
+        <v>0</v>
+      </c>
+      <c r="X23" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y23" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>300</v>
+      </c>
+      <c r="AB23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD23" t="inlineStr"/>
+      <c r="AE23" t="n">
+        <v>15</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>924</v>
+      </c>
+      <c r="AG23" t="inlineStr">
+        <is>
+          <t>Tarde</t>
+        </is>
+      </c>
+      <c r="AH23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK23" t="b">
+        <v>1</v>
+      </c>
+      <c r="AL23" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>16871592</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>PONTO ESTRATÉGICO</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>403 - JARDIM UNIVERSITARIO - PE</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Q023</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Avenida VINÍCIUS SOARES DO NASCIMENTO</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>410 - 1 - C</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Ponto Estratégico</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>12/08/2026 15:35</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>12/08/2026 15:51</t>
+        </is>
+      </c>
+      <c r="K24" t="n">
+        <v>1031</v>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>Antonio Cezar Marques</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>Ponto Estratégico</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="n">
+        <v>46246.64930555555</v>
+      </c>
+      <c r="O24" s="2" t="n">
+        <v>46246.66041666667</v>
+      </c>
+      <c r="P24" t="n">
+        <v>16</v>
+      </c>
+      <c r="Q24" s="3" t="n">
+        <v>46246</v>
+      </c>
+      <c r="R24" t="n">
+        <v>319</v>
+      </c>
+      <c r="S24" t="n">
+        <v>32</v>
+      </c>
+      <c r="T24" t="b">
+        <v>0</v>
+      </c>
+      <c r="U24" t="b">
+        <v>0</v>
+      </c>
+      <c r="V24" t="b">
+        <v>1</v>
+      </c>
+      <c r="W24" t="b">
+        <v>0</v>
+      </c>
+      <c r="X24" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y24" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>660</v>
+      </c>
+      <c r="AB24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD24" t="inlineStr"/>
+      <c r="AE24" t="n">
+        <v>15</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>935</v>
+      </c>
+      <c r="AG24" t="inlineStr">
+        <is>
+          <t>Tarde</t>
+        </is>
+      </c>
+      <c r="AH24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK24" t="b">
+        <v>1</v>
+      </c>
+      <c r="AL24" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>16883261</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>PONTO ESTRATÉGICO</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>408 - PARQUE DE EXPOSIÇOES - PE</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Q027</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Avenida PROCURADOR DR. WILSON DIAS DE PINHO</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>175 - 1 - C</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Ponto Estratégico</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>12/08/2026 15:43</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>12/08/2026 15:53</t>
+        </is>
+      </c>
+      <c r="K25" t="n">
+        <v>1031</v>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>Antonio Cezar Marques</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>Ponto Estratégico</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="n">
+        <v>46246.65486111111</v>
+      </c>
+      <c r="O25" s="2" t="n">
+        <v>46246.66180555556</v>
+      </c>
+      <c r="P25" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q25" s="3" t="n">
+        <v>46246</v>
+      </c>
+      <c r="R25" t="n">
+        <v>319</v>
+      </c>
+      <c r="S25" t="n">
+        <v>32</v>
+      </c>
+      <c r="T25" t="b">
+        <v>0</v>
+      </c>
+      <c r="U25" t="b">
+        <v>0</v>
+      </c>
+      <c r="V25" t="b">
+        <v>0</v>
+      </c>
+      <c r="W25" t="b">
+        <v>0</v>
+      </c>
+      <c r="X25" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y25" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>480</v>
+      </c>
+      <c r="AB25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD25" t="inlineStr"/>
+      <c r="AE25" t="n">
+        <v>15</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>943</v>
+      </c>
+      <c r="AG25" t="inlineStr">
+        <is>
+          <t>Tarde</t>
+        </is>
+      </c>
+      <c r="AH25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK25" t="b">
+        <v>1</v>
+      </c>
+      <c r="AL25" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>16883262</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>PONTO ESTRATÉGICO</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>408 - PARQUE DE EXPOSIÇOES - PE</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Q037</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Rua CORONEL PONCE</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>02 - OU</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Ponto Estratégico</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>12/08/2026 15:54</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>12/08/2026 16:07</t>
+        </is>
+      </c>
+      <c r="K26" t="n">
+        <v>1031</v>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>Antonio Cezar Marques</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>Ponto Estratégico</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="n">
+        <v>46246.6625</v>
+      </c>
+      <c r="O26" s="2" t="n">
+        <v>46246.67152777778</v>
+      </c>
+      <c r="P26" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q26" s="3" t="n">
+        <v>46246</v>
+      </c>
+      <c r="R26" t="n">
+        <v>319</v>
+      </c>
+      <c r="S26" t="n">
+        <v>32</v>
+      </c>
+      <c r="T26" t="b">
+        <v>0</v>
+      </c>
+      <c r="U26" t="b">
+        <v>0</v>
+      </c>
+      <c r="V26" t="b">
+        <v>0</v>
+      </c>
+      <c r="W26" t="b">
+        <v>0</v>
+      </c>
+      <c r="X26" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y26" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>660</v>
+      </c>
+      <c r="AB26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD26" t="inlineStr"/>
+      <c r="AE26" t="n">
+        <v>15</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>954</v>
+      </c>
+      <c r="AG26" t="inlineStr">
+        <is>
+          <t>Tarde</t>
+        </is>
+      </c>
+      <c r="AH26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK26" t="b">
+        <v>1</v>
+      </c>
+      <c r="AL26" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>16871593</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>PONTO ESTRATÉGICO</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>406 - JARDIM PRIMAVERA - PE</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Q030</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Rua VASCO DA GAMA</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>327 - 5 - C</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Ponto Estratégico</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>12/08/2026 15:57</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>12/08/2026 16:07</t>
+        </is>
+      </c>
+      <c r="K27" t="n">
+        <v>1031</v>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>Antonio Cezar Marques</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>Ponto Estratégico</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="n">
+        <v>46246.66458333333</v>
+      </c>
+      <c r="O27" s="2" t="n">
+        <v>46246.67152777778</v>
+      </c>
+      <c r="P27" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q27" s="3" t="n">
+        <v>46246</v>
+      </c>
+      <c r="R27" t="n">
+        <v>319</v>
+      </c>
+      <c r="S27" t="n">
+        <v>32</v>
+      </c>
+      <c r="T27" t="b">
+        <v>0</v>
+      </c>
+      <c r="U27" t="b">
+        <v>0</v>
+      </c>
+      <c r="V27" t="b">
+        <v>0</v>
+      </c>
+      <c r="W27" t="b">
+        <v>0</v>
+      </c>
+      <c r="X27" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y27" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>180</v>
+      </c>
+      <c r="AB27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD27" t="inlineStr"/>
+      <c r="AE27" t="n">
+        <v>15</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>957</v>
+      </c>
+      <c r="AG27" t="inlineStr">
+        <is>
+          <t>Tarde</t>
+        </is>
+      </c>
+      <c r="AH27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK27" t="b">
+        <v>1</v>
+      </c>
+      <c r="AL27" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>16899035</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>PONTO ESTRATÉGICO</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>403 - JARDIM UNIVERSITARIO - PE</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Q001</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Avenida VINÍCIUS SOARES DO NASCIMENTO</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>210 - C</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Ponto Estratégico</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>13/08/2026 14:56</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>13/08/2026 15:11</t>
+        </is>
+      </c>
+      <c r="K28" t="n">
+        <v>1031</v>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>Antonio Cezar Marques</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>Ponto Estratégico</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="n">
+        <v>46247.62222222222</v>
+      </c>
+      <c r="O28" s="2" t="n">
+        <v>46247.63263888889</v>
+      </c>
+      <c r="P28" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q28" s="3" t="n">
+        <v>46247</v>
+      </c>
+      <c r="R28" t="n">
+        <v>319</v>
+      </c>
+      <c r="S28" t="n">
+        <v>32</v>
+      </c>
+      <c r="T28" t="b">
+        <v>0</v>
+      </c>
+      <c r="U28" t="b">
+        <v>0</v>
+      </c>
+      <c r="V28" t="b">
+        <v>0</v>
+      </c>
+      <c r="W28" t="b">
+        <v>0</v>
+      </c>
+      <c r="X28" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y28" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>82740</v>
+      </c>
+      <c r="AB28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD28" t="inlineStr"/>
+      <c r="AE28" t="n">
+        <v>14</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>896</v>
+      </c>
+      <c r="AG28" t="inlineStr">
+        <is>
+          <t>Tarde</t>
+        </is>
+      </c>
+      <c r="AH28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK28" t="b">
+        <v>1</v>
+      </c>
+      <c r="AL28" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>16901238</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>PONTO ESTRATÉGICO</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>400 - JULIA CARDINAL- PE</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Q012</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Rua Anselmo Soares</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>28 - 1 - OU</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Ponto Estratégico</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>13/08/2026 15:20</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>13/08/2026 15:32</t>
+        </is>
+      </c>
+      <c r="K29" t="n">
+        <v>1031</v>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>Antonio Cezar Marques</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>Ponto Estratégico</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="n">
+        <v>46247.63888888889</v>
+      </c>
+      <c r="O29" s="2" t="n">
+        <v>46247.64722222222</v>
+      </c>
+      <c r="P29" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q29" s="3" t="n">
+        <v>46247</v>
+      </c>
+      <c r="R29" t="n">
+        <v>319</v>
+      </c>
+      <c r="S29" t="n">
+        <v>32</v>
+      </c>
+      <c r="T29" t="b">
+        <v>0</v>
+      </c>
+      <c r="U29" t="b">
+        <v>0</v>
+      </c>
+      <c r="V29" t="b">
+        <v>0</v>
+      </c>
+      <c r="W29" t="b">
+        <v>0</v>
+      </c>
+      <c r="X29" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y29" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>1440</v>
+      </c>
+      <c r="AB29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD29" t="inlineStr"/>
+      <c r="AE29" t="n">
+        <v>15</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>920</v>
+      </c>
+      <c r="AG29" t="inlineStr">
+        <is>
+          <t>Tarde</t>
+        </is>
+      </c>
+      <c r="AH29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK29" t="b">
+        <v>1</v>
+      </c>
+      <c r="AL29" t="b">
         <v>0</v>
       </c>
     </row>

--- a/data/semanas/319_pe.xlsx
+++ b/data/semanas/319_pe.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL29"/>
+  <dimension ref="A1:AL38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4490,6 +4490,1248 @@
         <v>1</v>
       </c>
       <c r="AL29" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>16913818</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>PONTO ESTRATÉGICO</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>400 - JULIA CARDINAL- PE</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Q002</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Rua MANOELA VIEIRA SOARES</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>999 - 1 - C</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Ponto Estratégico</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>13/08/2026 15:37</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>13/08/2026 16:02</t>
+        </is>
+      </c>
+      <c r="K30" t="n">
+        <v>1031</v>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>Antonio Cezar Marques</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>Ponto Estratégico</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="n">
+        <v>46247.65069444444</v>
+      </c>
+      <c r="O30" s="2" t="n">
+        <v>46247.66805555556</v>
+      </c>
+      <c r="P30" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q30" s="3" t="n">
+        <v>46247</v>
+      </c>
+      <c r="R30" t="n">
+        <v>319</v>
+      </c>
+      <c r="S30" t="n">
+        <v>32</v>
+      </c>
+      <c r="T30" t="b">
+        <v>0</v>
+      </c>
+      <c r="U30" t="b">
+        <v>0</v>
+      </c>
+      <c r="V30" t="b">
+        <v>1</v>
+      </c>
+      <c r="W30" t="b">
+        <v>0</v>
+      </c>
+      <c r="X30" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y30" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>1020</v>
+      </c>
+      <c r="AB30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD30" t="inlineStr"/>
+      <c r="AE30" t="n">
+        <v>15</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>937</v>
+      </c>
+      <c r="AG30" t="inlineStr">
+        <is>
+          <t>Tarde</t>
+        </is>
+      </c>
+      <c r="AH30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK30" t="b">
+        <v>1</v>
+      </c>
+      <c r="AL30" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>16919472</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>PONTO ESTRATÉGICO</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>410 SALGADO FILHO PE</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Q008</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Rua ENGENHEIRO MAURICIO DUTRA</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>273 - C</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Ponto Estratégico</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>14/08/2026 08:53</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>14/08/2026 08:58</t>
+        </is>
+      </c>
+      <c r="K31" t="n">
+        <v>1031</v>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>Antonio Cezar Marques</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>Ponto Estratégico</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="n">
+        <v>46248.37013888889</v>
+      </c>
+      <c r="O31" s="2" t="n">
+        <v>46248.37361111111</v>
+      </c>
+      <c r="P31" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q31" s="3" t="n">
+        <v>46248</v>
+      </c>
+      <c r="R31" t="n">
+        <v>319</v>
+      </c>
+      <c r="S31" t="n">
+        <v>32</v>
+      </c>
+      <c r="T31" t="b">
+        <v>0</v>
+      </c>
+      <c r="U31" t="b">
+        <v>0</v>
+      </c>
+      <c r="V31" t="b">
+        <v>0</v>
+      </c>
+      <c r="W31" t="b">
+        <v>0</v>
+      </c>
+      <c r="X31" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y31" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>62160</v>
+      </c>
+      <c r="AB31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD31" t="inlineStr"/>
+      <c r="AE31" t="n">
+        <v>8</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>533</v>
+      </c>
+      <c r="AG31" t="inlineStr">
+        <is>
+          <t>Manhã</t>
+        </is>
+      </c>
+      <c r="AH31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>4</v>
+      </c>
+      <c r="AJ31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK31" t="b">
+        <v>1</v>
+      </c>
+      <c r="AL31" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>16919469</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>PONTO ESTRATÉGICO</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>448 - SANGA II -PE</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Q045</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Rodovia BR 463</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>09 - C</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Ponto Estratégico</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>14/08/2026 09:05</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>14/08/2026 09:21</t>
+        </is>
+      </c>
+      <c r="K32" t="n">
+        <v>1031</v>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>Antonio Cezar Marques</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>Ponto Estratégico</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="n">
+        <v>46248.37847222222</v>
+      </c>
+      <c r="O32" s="2" t="n">
+        <v>46248.38958333333</v>
+      </c>
+      <c r="P32" t="n">
+        <v>16</v>
+      </c>
+      <c r="Q32" s="3" t="n">
+        <v>46248</v>
+      </c>
+      <c r="R32" t="n">
+        <v>319</v>
+      </c>
+      <c r="S32" t="n">
+        <v>32</v>
+      </c>
+      <c r="T32" t="b">
+        <v>0</v>
+      </c>
+      <c r="U32" t="b">
+        <v>0</v>
+      </c>
+      <c r="V32" t="b">
+        <v>1</v>
+      </c>
+      <c r="W32" t="b">
+        <v>0</v>
+      </c>
+      <c r="X32" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y32" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>720</v>
+      </c>
+      <c r="AB32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD32" t="inlineStr"/>
+      <c r="AE32" t="n">
+        <v>9</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>545</v>
+      </c>
+      <c r="AG32" t="inlineStr">
+        <is>
+          <t>Manhã</t>
+        </is>
+      </c>
+      <c r="AH32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>4</v>
+      </c>
+      <c r="AJ32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK32" t="b">
+        <v>1</v>
+      </c>
+      <c r="AL32" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>16919473</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>PONTO ESTRATÉGICO</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>447 - SANGA I - PE</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Q002</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Avenida INTERNACIONAL SP</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>99 - 3 - C</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Ponto Estratégico</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>14/08/2026 09:19</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>14/08/2026 09:34</t>
+        </is>
+      </c>
+      <c r="K33" t="n">
+        <v>1031</v>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>Antonio Cezar Marques</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>Ponto Estratégico</t>
+        </is>
+      </c>
+      <c r="N33" s="2" t="n">
+        <v>46248.38819444444</v>
+      </c>
+      <c r="O33" s="2" t="n">
+        <v>46248.39861111111</v>
+      </c>
+      <c r="P33" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q33" s="3" t="n">
+        <v>46248</v>
+      </c>
+      <c r="R33" t="n">
+        <v>319</v>
+      </c>
+      <c r="S33" t="n">
+        <v>32</v>
+      </c>
+      <c r="T33" t="b">
+        <v>0</v>
+      </c>
+      <c r="U33" t="b">
+        <v>0</v>
+      </c>
+      <c r="V33" t="b">
+        <v>0</v>
+      </c>
+      <c r="W33" t="b">
+        <v>0</v>
+      </c>
+      <c r="X33" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y33" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>840</v>
+      </c>
+      <c r="AB33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD33" t="inlineStr"/>
+      <c r="AE33" t="n">
+        <v>9</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>559</v>
+      </c>
+      <c r="AG33" t="inlineStr">
+        <is>
+          <t>Manhã</t>
+        </is>
+      </c>
+      <c r="AH33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI33" t="n">
+        <v>4</v>
+      </c>
+      <c r="AJ33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK33" t="b">
+        <v>1</v>
+      </c>
+      <c r="AL33" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>16919470</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>PONTO ESTRATÉGICO</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>447 - SANGA I - PE</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Q023</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Avenida INTERNACIONAL SP</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2577 - C</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Ponto Estratégico</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>14/08/2026 09:29</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>14/08/2026 09:43</t>
+        </is>
+      </c>
+      <c r="K34" t="n">
+        <v>1031</v>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>Antonio Cezar Marques</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>Ponto Estratégico</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="n">
+        <v>46248.39513888889</v>
+      </c>
+      <c r="O34" s="2" t="n">
+        <v>46248.40486111111</v>
+      </c>
+      <c r="P34" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q34" s="3" t="n">
+        <v>46248</v>
+      </c>
+      <c r="R34" t="n">
+        <v>319</v>
+      </c>
+      <c r="S34" t="n">
+        <v>32</v>
+      </c>
+      <c r="T34" t="b">
+        <v>0</v>
+      </c>
+      <c r="U34" t="b">
+        <v>0</v>
+      </c>
+      <c r="V34" t="b">
+        <v>0</v>
+      </c>
+      <c r="W34" t="b">
+        <v>0</v>
+      </c>
+      <c r="X34" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y34" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>600</v>
+      </c>
+      <c r="AB34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD34" t="inlineStr"/>
+      <c r="AE34" t="n">
+        <v>9</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>569</v>
+      </c>
+      <c r="AG34" t="inlineStr">
+        <is>
+          <t>Manhã</t>
+        </is>
+      </c>
+      <c r="AH34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI34" t="n">
+        <v>4</v>
+      </c>
+      <c r="AJ34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK34" t="b">
+        <v>1</v>
+      </c>
+      <c r="AL34" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>16919475</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>PONTO ESTRATÉGICO</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>447 - SANGA I - PE</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Q035</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Avenida INTERNACIONAL SP</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2663 - C</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Ponto Estratégico</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>14/08/2026 09:33</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>14/08/2026 09:44</t>
+        </is>
+      </c>
+      <c r="K35" t="n">
+        <v>1031</v>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>Antonio Cezar Marques</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>Ponto Estratégico</t>
+        </is>
+      </c>
+      <c r="N35" s="2" t="n">
+        <v>46248.39791666667</v>
+      </c>
+      <c r="O35" s="2" t="n">
+        <v>46248.40555555555</v>
+      </c>
+      <c r="P35" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q35" s="3" t="n">
+        <v>46248</v>
+      </c>
+      <c r="R35" t="n">
+        <v>319</v>
+      </c>
+      <c r="S35" t="n">
+        <v>32</v>
+      </c>
+      <c r="T35" t="b">
+        <v>0</v>
+      </c>
+      <c r="U35" t="b">
+        <v>0</v>
+      </c>
+      <c r="V35" t="b">
+        <v>0</v>
+      </c>
+      <c r="W35" t="b">
+        <v>0</v>
+      </c>
+      <c r="X35" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y35" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>240</v>
+      </c>
+      <c r="AB35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD35" t="inlineStr"/>
+      <c r="AE35" t="n">
+        <v>9</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>573</v>
+      </c>
+      <c r="AG35" t="inlineStr">
+        <is>
+          <t>Manhã</t>
+        </is>
+      </c>
+      <c r="AH35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI35" t="n">
+        <v>4</v>
+      </c>
+      <c r="AJ35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK35" t="b">
+        <v>1</v>
+      </c>
+      <c r="AL35" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>16919474</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>PONTO ESTRATÉGICO</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>447 - SANGA I - PE</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Q035</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Avenida INTERNACIONAL SP</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>266 - C</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Ponto Estratégico</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>14/08/2026 09:37</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>14/08/2026 09:55</t>
+        </is>
+      </c>
+      <c r="K36" t="n">
+        <v>1031</v>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>Antonio Cezar Marques</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>Ponto Estratégico</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="n">
+        <v>46248.40069444444</v>
+      </c>
+      <c r="O36" s="2" t="n">
+        <v>46248.41319444445</v>
+      </c>
+      <c r="P36" t="n">
+        <v>18</v>
+      </c>
+      <c r="Q36" s="3" t="n">
+        <v>46248</v>
+      </c>
+      <c r="R36" t="n">
+        <v>319</v>
+      </c>
+      <c r="S36" t="n">
+        <v>32</v>
+      </c>
+      <c r="T36" t="b">
+        <v>0</v>
+      </c>
+      <c r="U36" t="b">
+        <v>0</v>
+      </c>
+      <c r="V36" t="b">
+        <v>1</v>
+      </c>
+      <c r="W36" t="b">
+        <v>0</v>
+      </c>
+      <c r="X36" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y36" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>240</v>
+      </c>
+      <c r="AB36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD36" t="inlineStr"/>
+      <c r="AE36" t="n">
+        <v>9</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>577</v>
+      </c>
+      <c r="AG36" t="inlineStr">
+        <is>
+          <t>Manhã</t>
+        </is>
+      </c>
+      <c r="AH36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI36" t="n">
+        <v>4</v>
+      </c>
+      <c r="AJ36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK36" t="b">
+        <v>1</v>
+      </c>
+      <c r="AL36" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>16919471</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>PONTO ESTRATÉGICO</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>448 - SANGA II -PE</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Q045</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Rodovia BR 463</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>08 - C</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Ponto Estratégico</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>14/08/2026 09:51</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>14/08/2026 10:06</t>
+        </is>
+      </c>
+      <c r="K37" t="n">
+        <v>1031</v>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>Antonio Cezar Marques</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>Ponto Estratégico</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="n">
+        <v>46248.41041666667</v>
+      </c>
+      <c r="O37" s="2" t="n">
+        <v>46248.42083333333</v>
+      </c>
+      <c r="P37" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q37" s="3" t="n">
+        <v>46248</v>
+      </c>
+      <c r="R37" t="n">
+        <v>319</v>
+      </c>
+      <c r="S37" t="n">
+        <v>32</v>
+      </c>
+      <c r="T37" t="b">
+        <v>0</v>
+      </c>
+      <c r="U37" t="b">
+        <v>0</v>
+      </c>
+      <c r="V37" t="b">
+        <v>0</v>
+      </c>
+      <c r="W37" t="b">
+        <v>0</v>
+      </c>
+      <c r="X37" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y37" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>840</v>
+      </c>
+      <c r="AB37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD37" t="inlineStr"/>
+      <c r="AE37" t="n">
+        <v>9</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>591</v>
+      </c>
+      <c r="AG37" t="inlineStr">
+        <is>
+          <t>Manhã</t>
+        </is>
+      </c>
+      <c r="AH37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI37" t="n">
+        <v>4</v>
+      </c>
+      <c r="AJ37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK37" t="b">
+        <v>1</v>
+      </c>
+      <c r="AL37" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>16919468</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>PONTO ESTRATÉGICO</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>448 - SANGA II -PE</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Q011</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Avenida NATALICIO ANTUNES DA SILVA</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>270 - 5 - OU</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Ponto Estratégico</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>14/08/2026 10:14</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>14/08/2026 10:20</t>
+        </is>
+      </c>
+      <c r="K38" t="n">
+        <v>1031</v>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>Antonio Cezar Marques</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>Ponto Estratégico</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="n">
+        <v>46248.42638888889</v>
+      </c>
+      <c r="O38" s="2" t="n">
+        <v>46248.43055555555</v>
+      </c>
+      <c r="P38" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q38" s="3" t="n">
+        <v>46248</v>
+      </c>
+      <c r="R38" t="n">
+        <v>319</v>
+      </c>
+      <c r="S38" t="n">
+        <v>32</v>
+      </c>
+      <c r="T38" t="b">
+        <v>0</v>
+      </c>
+      <c r="U38" t="b">
+        <v>0</v>
+      </c>
+      <c r="V38" t="b">
+        <v>0</v>
+      </c>
+      <c r="W38" t="b">
+        <v>0</v>
+      </c>
+      <c r="X38" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y38" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>1380</v>
+      </c>
+      <c r="AB38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AC38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD38" t="inlineStr"/>
+      <c r="AE38" t="n">
+        <v>10</v>
+      </c>
+      <c r="AF38" t="n">
+        <v>614</v>
+      </c>
+      <c r="AG38" t="inlineStr">
+        <is>
+          <t>Manhã</t>
+        </is>
+      </c>
+      <c r="AH38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI38" t="n">
+        <v>4</v>
+      </c>
+      <c r="AJ38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK38" t="b">
+        <v>1</v>
+      </c>
+      <c r="AL38" t="b">
         <v>0</v>
       </c>
     </row>
